--- a/AY23-24/COD/ReportFormats/PGYR24OP_Format.xlsx
+++ b/AY23-24/COD/ReportFormats/PGYR24OP_Format.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robertpatton/Repositories/FASolutions/FSADocumentation/AY23-24/COD/ReportFormats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93562E8-4C30-A74C-B8B9-3B8DF93D7942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE90F43-3158-9D4B-A081-EEDA64E56380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19620" yWindow="740" windowWidth="13980" windowHeight="20260" xr2:uid="{598557D2-139C-CF48-8435-AE8D090B2F2A}"/>
+    <workbookView xWindow="36860" yWindow="820" windowWidth="13980" windowHeight="20260" xr2:uid="{598557D2-139C-CF48-8435-AE8D090B2F2A}"/>
   </bookViews>
   <sheets>
     <sheet name="PGYR24OP" sheetId="1" r:id="rId1"/>
@@ -140,9 +140,6 @@
     <t>StudentFirstName</t>
   </si>
   <si>
-    <t>StudentMIddleInitial</t>
-  </si>
-  <si>
     <t>StudentSSN</t>
   </si>
   <si>
@@ -170,9 +167,6 @@
     <t>0000000, last 3 digits indicate less than 1 percent, no decimal point</t>
   </si>
   <si>
-    <t>ProgramCIPCode</t>
-  </si>
-  <si>
     <t>format is 00.0000 - 99.0000</t>
   </si>
   <si>
@@ -182,36 +176,18 @@
     <t>"F" = full-time, "Q" = three-quarters time, "H" = half-time, "L" = less than half-time</t>
   </si>
   <si>
-    <t>PublishedProgramLengthYears</t>
-  </si>
-  <si>
-    <t>PublishedProgramLengthMonths</t>
-  </si>
-  <si>
-    <t>PublishedProgramLengthWeeks</t>
-  </si>
-  <si>
     <t>00V000 to 99V000, or blank. Decimal is implied</t>
   </si>
   <si>
     <t>000V000 to 999V000, or blank. Decimal is implied</t>
   </si>
   <si>
-    <t>SpecialProgramIndicator</t>
-  </si>
-  <si>
     <t>"A" = Selective Admission Associate Program, "B" = Bachelor's Degree Completion Program, "N" = Not applicable, "P" = Preparatory Coursework Graduate Professional Program, "T" = Non-credential Teacher Certification Program, "U" = Prparatory Coursework Undergraduate Program</t>
   </si>
   <si>
-    <t>ProgramCredentialLevel</t>
-  </si>
-  <si>
     <t>01 = Undergraduate certificate or diploma, 02 = Associate degree, 03 = Bachelor's degree, 04 = Post Baccalaureate certificate</t>
   </si>
   <si>
-    <t>WeeksProgramsAcademicYear</t>
-  </si>
-  <si>
     <t>000V000 to 999V999, total number of weeks of instruction in the program's academic year</t>
   </si>
   <si>
@@ -231,6 +207,30 @@
   </si>
   <si>
     <t>Filler4</t>
+  </si>
+  <si>
+    <t>ProgramCIPCode1</t>
+  </si>
+  <si>
+    <t>StudentMiddleName</t>
+  </si>
+  <si>
+    <t>SpecialProgramIndicator1</t>
+  </si>
+  <si>
+    <t>ProgramCredentialLevel1</t>
+  </si>
+  <si>
+    <t>WeeksProgramsAcademicYear1</t>
+  </si>
+  <si>
+    <t>PublishedProgramLengthYears1</t>
+  </si>
+  <si>
+    <t>PublishedProgramLengthMonths1</t>
+  </si>
+  <si>
+    <t>PublishedProgramLengthWeeks1</t>
   </si>
 </sst>
 </file>
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -1020,7 +1020,7 @@
         <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -1037,7 +1037,7 @@
         <v>8</v>
       </c>
       <c r="E23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F23" t="s">
         <v>8</v>
@@ -1057,10 +1057,10 @@
         <v>2</v>
       </c>
       <c r="E24" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" t="s">
         <v>37</v>
-      </c>
-      <c r="F24" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
@@ -1077,10 +1077,10 @@
         <v>1</v>
       </c>
       <c r="E25" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" t="s">
         <v>39</v>
-      </c>
-      <c r="F25" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
@@ -1097,7 +1097,7 @@
         <v>2</v>
       </c>
       <c r="E26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
@@ -1114,10 +1114,10 @@
         <v>7</v>
       </c>
       <c r="E27" t="s">
+        <v>41</v>
+      </c>
+      <c r="F27" t="s">
         <v>42</v>
-      </c>
-      <c r="F27" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -1134,10 +1134,10 @@
         <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="F28" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
@@ -1154,10 +1154,10 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -1174,10 +1174,10 @@
         <v>5</v>
       </c>
       <c r="E30" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="F30" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -1194,10 +1194,10 @@
         <v>5</v>
       </c>
       <c r="E31" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="F31" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -1214,10 +1214,10 @@
         <v>6</v>
       </c>
       <c r="E32" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="F32" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
@@ -1234,10 +1234,10 @@
         <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F33" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -1254,10 +1254,10 @@
         <v>2</v>
       </c>
       <c r="E34" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F34" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
@@ -1274,10 +1274,10 @@
         <v>6</v>
       </c>
       <c r="E35" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F35" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
@@ -1294,10 +1294,10 @@
         <v>4</v>
       </c>
       <c r="E36" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="F36" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
@@ -1314,7 +1314,7 @@
         <v>8</v>
       </c>
       <c r="E37" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F37" t="s">
         <v>8</v>
@@ -1334,10 +1334,10 @@
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="F38" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
@@ -1354,7 +1354,7 @@
         <v>91</v>
       </c>
       <c r="E39" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
